--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.28066050162797</v>
+        <v>4.270607331514546</v>
       </c>
       <c r="D2" t="n">
-        <v>25.84533995028303</v>
+        <v>4.199867741920992</v>
       </c>
       <c r="E2" t="n">
-        <v>8.021492706444532</v>
+        <v>1.303492564797236</v>
       </c>
       <c r="F2" t="n">
-        <v>8.182031366489145</v>
+        <v>1.329580097054486</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.72902981582708</v>
+        <v>7.4309673450719</v>
       </c>
       <c r="D3" t="n">
-        <v>46.19594832134992</v>
+        <v>7.506841602219363</v>
       </c>
       <c r="E3" t="n">
-        <v>8.021492706444532</v>
+        <v>1.303492564797236</v>
       </c>
       <c r="F3" t="n">
-        <v>8.182031366489145</v>
+        <v>1.329580097054486</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.50627817956495</v>
+        <v>5.119770204179305</v>
       </c>
       <c r="D4" t="n">
-        <v>30.02420179130319</v>
+        <v>4.878932791086768</v>
       </c>
       <c r="E4" t="n">
-        <v>8.021492706444532</v>
+        <v>1.303492564797236</v>
       </c>
       <c r="F4" t="n">
-        <v>8.182031366489145</v>
+        <v>1.329580097054486</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.07005420470636</v>
+        <v>3.586383808264784</v>
       </c>
       <c r="D5" t="n">
-        <v>22.96683238096697</v>
+        <v>3.732110261907132</v>
       </c>
       <c r="E5" t="n">
-        <v>8.021492706444532</v>
+        <v>1.303492564797236</v>
       </c>
       <c r="F5" t="n">
-        <v>8.182031366489145</v>
+        <v>1.329580097054486</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.55940596464264</v>
+        <v>4.478403469254428</v>
       </c>
       <c r="D6" t="n">
-        <v>25.98949443311449</v>
+        <v>4.223292845381104</v>
       </c>
       <c r="E6" t="n">
-        <v>8.021492706444532</v>
+        <v>1.303492564797236</v>
       </c>
       <c r="F6" t="n">
-        <v>8.182031366489145</v>
+        <v>1.329580097054486</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.36103921358923</v>
+        <v>3.47116887220825</v>
       </c>
       <c r="D7" t="n">
-        <v>22.93406575358412</v>
+        <v>3.72678568495742</v>
       </c>
       <c r="E7" t="n">
-        <v>8.021492706444532</v>
+        <v>1.303492564797236</v>
       </c>
       <c r="F7" t="n">
-        <v>8.182031366489145</v>
+        <v>1.329580097054486</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.34108678304391</v>
+        <v>2.980426602244635</v>
       </c>
       <c r="D8" t="n">
-        <v>16.83705113605711</v>
+        <v>2.736020809609281</v>
       </c>
       <c r="E8" t="n">
-        <v>8.021492706444532</v>
+        <v>1.303492564797236</v>
       </c>
       <c r="F8" t="n">
-        <v>8.182031366489145</v>
+        <v>1.329580097054486</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.6484822890992</v>
+        <v>5.46787837197862</v>
       </c>
       <c r="D9" t="n">
-        <v>35.44590996452415</v>
+        <v>5.759960369235174</v>
       </c>
       <c r="E9" t="n">
-        <v>8.021492706444532</v>
+        <v>1.303492564797236</v>
       </c>
       <c r="F9" t="n">
-        <v>8.182031366489145</v>
+        <v>1.329580097054486</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>21.14370473519598</v>
+        <v>3.435852019469347</v>
       </c>
       <c r="D10" t="n">
-        <v>22.64604248847958</v>
+        <v>3.679981904377932</v>
       </c>
       <c r="E10" t="n">
-        <v>8.021492706444532</v>
+        <v>1.303492564797236</v>
       </c>
       <c r="F10" t="n">
-        <v>8.182031366489145</v>
+        <v>1.329580097054486</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
